--- a/CS6735_PROJECT_COMPLETE.xlsx
+++ b/CS6735_PROJECT_COMPLETE.xlsx
@@ -11956,27 +11956,27 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -12026,27 +12026,27 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.001}</t>
         </is>
       </c>
     </row>
@@ -12096,27 +12096,27 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -12166,27 +12166,27 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -12236,27 +12236,27 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -12306,27 +12306,27 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -12376,27 +12376,27 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.001}</t>
         </is>
       </c>
     </row>
@@ -12446,27 +12446,27 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -12516,27 +12516,27 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -12586,27 +12586,27 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -12750,27 +12750,27 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -12820,27 +12820,27 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -12890,27 +12890,27 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -12960,27 +12960,27 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -13030,27 +13030,27 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -13100,27 +13100,27 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.001}</t>
         </is>
       </c>
     </row>
@@ -13170,27 +13170,27 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -13240,27 +13240,27 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -13310,27 +13310,27 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 7}</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -13380,27 +13380,27 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -13544,27 +13544,27 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -13614,27 +13614,27 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -13684,27 +13684,27 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.001}</t>
         </is>
       </c>
     </row>
@@ -13754,27 +13754,27 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 5}</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 5, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -13824,27 +13824,27 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -13894,27 +13894,27 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 7}</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 5, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -13964,27 +13964,27 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -14034,27 +14034,27 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5}</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -14104,27 +14104,27 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -14174,27 +14174,27 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.001}</t>
         </is>
       </c>
     </row>
@@ -14338,27 +14338,27 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -14408,27 +14408,27 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -14478,27 +14478,27 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 7}</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 5, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -14548,27 +14548,27 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -14618,27 +14618,27 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 9}</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -14688,27 +14688,27 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.001}</t>
         </is>
       </c>
     </row>
@@ -14758,27 +14758,27 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 9}</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -14828,27 +14828,27 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 11}</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 3, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 5, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -14898,27 +14898,27 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -14968,27 +14968,27 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.001}</t>
         </is>
       </c>
     </row>
@@ -15132,27 +15132,27 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -15202,27 +15202,27 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -15272,27 +15272,27 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -15342,27 +15342,27 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -15412,27 +15412,27 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -15482,27 +15482,27 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -15552,27 +15552,27 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -15622,27 +15622,27 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -15692,27 +15692,27 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -15762,27 +15762,27 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -15926,27 +15926,27 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -15996,27 +15996,27 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -16066,27 +16066,27 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -16136,27 +16136,27 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -16206,27 +16206,27 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -16276,27 +16276,27 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -16346,27 +16346,27 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -16416,27 +16416,27 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -16486,27 +16486,27 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -16556,27 +16556,27 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -16720,27 +16720,27 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -16790,27 +16790,27 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -16860,27 +16860,27 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 5}</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.001}</t>
         </is>
       </c>
     </row>
@@ -16930,27 +16930,27 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -17000,27 +17000,27 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 5, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -17070,27 +17070,27 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 5, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -17140,27 +17140,27 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 5, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.001}</t>
         </is>
       </c>
     </row>
@@ -17210,27 +17210,27 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 5}</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -17280,27 +17280,27 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -17350,27 +17350,27 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -17514,27 +17514,27 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -17584,27 +17584,27 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -17654,27 +17654,27 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 5}</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.001}</t>
         </is>
       </c>
     </row>
@@ -17724,27 +17724,27 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -17794,27 +17794,27 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 5, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -17864,27 +17864,27 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 5, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -17934,27 +17934,27 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 5, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.001}</t>
         </is>
       </c>
     </row>
@@ -18004,27 +18004,27 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 5}</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -18074,27 +18074,27 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -18144,27 +18144,27 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'rbf', 'C': 10, 'gamma': 'scale'}</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -18308,27 +18308,27 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 0.1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -18378,27 +18378,27 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 10, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -18448,27 +18448,27 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 5, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -18518,27 +18518,27 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 10, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -18588,27 +18588,27 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 0.1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -18658,27 +18658,27 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 10, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -18728,27 +18728,27 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -18798,27 +18798,27 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -18868,27 +18868,27 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 0.1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 7}</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -18938,27 +18938,27 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 0.1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -19102,27 +19102,27 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 5, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -19172,27 +19172,27 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 0.1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 5, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -19242,27 +19242,27 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 7}</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -19312,27 +19312,27 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 0.1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 5}</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -19382,27 +19382,27 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -19452,27 +19452,27 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 10, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -19522,27 +19522,27 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 0.1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.001}</t>
         </is>
       </c>
     </row>
@@ -19592,27 +19592,27 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 0.1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5}</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -19662,27 +19662,27 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 0.1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5}</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -19732,27 +19732,27 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 0.1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -19896,27 +19896,27 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 0.1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 7}</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 5, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -19966,27 +19966,27 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 0.1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5}</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -20036,27 +20036,27 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 0.1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 7}</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -20106,27 +20106,27 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 0.1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 7}</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -20176,27 +20176,27 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 0.1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 5}</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 5, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -20246,27 +20246,27 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 7}</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -20316,27 +20316,27 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 7}</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -20386,27 +20386,27 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 0.1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 7}</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 5, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -20456,27 +20456,27 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 0.1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -20526,27 +20526,27 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -20690,27 +20690,27 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 10, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 5}</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -20760,27 +20760,27 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 0.1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 11}</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 5, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -20830,27 +20830,27 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 5}</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -20900,27 +20900,27 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -20970,27 +20970,27 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -21040,27 +21040,27 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 0.1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 11}</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -21110,27 +21110,27 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 0.1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 5}</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -21180,27 +21180,27 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 10, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 7}</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -21250,27 +21250,27 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -21320,27 +21320,27 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 11}</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -21484,27 +21484,27 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 10, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -21554,27 +21554,27 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -21624,27 +21624,27 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 0.1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -21694,27 +21694,27 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 5, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -21764,27 +21764,27 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 0.1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5}</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -21834,27 +21834,27 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 5, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -21904,27 +21904,27 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 10, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -21974,27 +21974,27 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -22044,27 +22044,27 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 0.1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -22114,27 +22114,27 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 10, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 9}</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -22278,27 +22278,27 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 10, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -22348,27 +22348,27 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -22418,27 +22418,27 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 0.1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -22488,27 +22488,27 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 5, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -22558,27 +22558,27 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 0.1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5}</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -22628,27 +22628,27 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 5, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -22698,27 +22698,27 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 10, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -22768,27 +22768,27 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -22838,27 +22838,27 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 0.1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -22908,27 +22908,27 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 10, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 9}</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -23072,27 +23072,27 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 0.1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -23142,27 +23142,27 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 10, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -23212,27 +23212,27 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 0.1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -23282,27 +23282,27 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -23352,27 +23352,27 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 10, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5}</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -23422,27 +23422,27 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -23492,27 +23492,27 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 7}</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -23562,27 +23562,27 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 0.1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -23632,27 +23632,27 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 0.1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -23702,27 +23702,27 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -23866,27 +23866,27 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 0.1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -23936,27 +23936,27 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 10, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -24006,27 +24006,27 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 0.1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -24076,27 +24076,27 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -24146,27 +24146,27 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 10, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5}</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -24216,27 +24216,27 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -24286,27 +24286,27 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 7}</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (128,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -24356,27 +24356,27 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 0.1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q190" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -24426,27 +24426,27 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 0.1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>
@@ -24496,27 +24496,27 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'kernel': 'linear', 'C': 1, 'gamma': 'N/A'}</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3}</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>RF permutation importance | n_repeats=10 | threshold=mean importance</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64, 64), 'learning_rate_init': 0.01}</t>
         </is>
       </c>
     </row>

--- a/CS6735_PROJECT_COMPLETE.xlsx
+++ b/CS6735_PROJECT_COMPLETE.xlsx
@@ -6177,10 +6177,10 @@
         <v>0.8901</v>
       </c>
       <c r="F99" t="n">
-        <v>0.9808</v>
+        <v>0.9856</v>
       </c>
       <c r="G99" t="n">
-        <v>0.8822</v>
+        <v>0.9232</v>
       </c>
       <c r="H99" t="n">
         <v>0.9916</v>
@@ -6239,10 +6239,10 @@
         <v>0.8226</v>
       </c>
       <c r="F100" t="n">
-        <v>0.9796</v>
+        <v>0.9808</v>
       </c>
       <c r="G100" t="n">
-        <v>0.8436</v>
+        <v>0.8408</v>
       </c>
       <c r="H100" t="n">
         <v>0.9892</v>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 5}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -6301,10 +6301,10 @@
         <v>0.8155</v>
       </c>
       <c r="F101" t="n">
-        <v>0.9808</v>
+        <v>0.9832</v>
       </c>
       <c r="G101" t="n">
-        <v>0.8843</v>
+        <v>0.8672</v>
       </c>
       <c r="H101" t="n">
         <v>0.9916</v>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -6366,7 +6366,7 @@
         <v>0.988</v>
       </c>
       <c r="G102" t="n">
-        <v>0.9026</v>
+        <v>0.907</v>
       </c>
       <c r="H102" t="n">
         <v>0.9868</v>
@@ -6392,7 +6392,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -6425,10 +6425,10 @@
         <v>0.7255</v>
       </c>
       <c r="F103" t="n">
-        <v>0.9844000000000001</v>
+        <v>0.9772</v>
       </c>
       <c r="G103" t="n">
-        <v>0.8707</v>
+        <v>0.8345</v>
       </c>
       <c r="H103" t="n">
         <v>0.9916</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -6487,10 +6487,10 @@
         <v>0.7104</v>
       </c>
       <c r="F104" t="n">
-        <v>0.9844000000000001</v>
+        <v>0.9772</v>
       </c>
       <c r="G104" t="n">
-        <v>0.8296</v>
+        <v>0.7853</v>
       </c>
       <c r="H104" t="n">
         <v>0.988</v>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -6552,7 +6552,7 @@
         <v>0.988</v>
       </c>
       <c r="G105" t="n">
-        <v>0.9176</v>
+        <v>0.8866000000000001</v>
       </c>
       <c r="H105" t="n">
         <v>0.9928</v>
@@ -6611,10 +6611,10 @@
         <v>0.864</v>
       </c>
       <c r="F106" t="n">
-        <v>0.9856</v>
+        <v>0.9868</v>
       </c>
       <c r="G106" t="n">
-        <v>0.8881</v>
+        <v>0.9041</v>
       </c>
       <c r="H106" t="n">
         <v>0.9928</v>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 5}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -6673,10 +6673,10 @@
         <v>0.8103</v>
       </c>
       <c r="F107" t="n">
-        <v>0.9772</v>
+        <v>0.9784</v>
       </c>
       <c r="G107" t="n">
-        <v>0.8282</v>
+        <v>0.833</v>
       </c>
       <c r="H107" t="n">
         <v>0.9856</v>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_split': 5}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -6735,10 +6735,10 @@
         <v>0.7812</v>
       </c>
       <c r="F108" t="n">
-        <v>0.9844000000000001</v>
+        <v>0.988</v>
       </c>
       <c r="G108" t="n">
-        <v>0.9079</v>
+        <v>0.9161</v>
       </c>
       <c r="H108" t="n">
         <v>0.9903999999999999</v>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 5}</t>
+          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -6878,13 +6878,13 @@
         <v>0.9232</v>
       </c>
       <c r="E111" t="n">
-        <v>0.442</v>
+        <v>0.4432</v>
       </c>
       <c r="F111" t="n">
-        <v>0.9448</v>
+        <v>0.9472</v>
       </c>
       <c r="G111" t="n">
-        <v>0.5139</v>
+        <v>0.5213</v>
       </c>
       <c r="H111" t="n">
         <v>0.952</v>
@@ -6946,7 +6946,7 @@
         <v>0.9364</v>
       </c>
       <c r="G112" t="n">
-        <v>0.3818</v>
+        <v>0.4236</v>
       </c>
       <c r="H112" t="n">
         <v>0.946</v>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 10}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -7005,10 +7005,10 @@
         <v>0.4916</v>
       </c>
       <c r="F113" t="n">
-        <v>0.9436</v>
+        <v>0.9412</v>
       </c>
       <c r="G113" t="n">
-        <v>0.5253</v>
+        <v>0.4906</v>
       </c>
       <c r="H113" t="n">
         <v>0.9472</v>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -7067,10 +7067,10 @@
         <v>0.4648</v>
       </c>
       <c r="F114" t="n">
-        <v>0.9352</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="G114" t="n">
-        <v>0.4178</v>
+        <v>0.418</v>
       </c>
       <c r="H114" t="n">
         <v>0.946</v>
@@ -7129,10 +7129,10 @@
         <v>0.4839</v>
       </c>
       <c r="F115" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.9292</v>
       </c>
       <c r="G115" t="n">
-        <v>0.4597</v>
+        <v>0.4422</v>
       </c>
       <c r="H115" t="n">
         <v>0.9484</v>
@@ -7158,7 +7158,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -7191,10 +7191,10 @@
         <v>0.4837</v>
       </c>
       <c r="F116" t="n">
-        <v>0.9388</v>
+        <v>0.928</v>
       </c>
       <c r="G116" t="n">
-        <v>0.488</v>
+        <v>0.4749</v>
       </c>
       <c r="H116" t="n">
         <v>0.9436</v>
@@ -7220,7 +7220,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -7253,10 +7253,10 @@
         <v>0.4459</v>
       </c>
       <c r="F117" t="n">
-        <v>0.946</v>
+        <v>0.9484</v>
       </c>
       <c r="G117" t="n">
-        <v>0.4332</v>
+        <v>0.4486</v>
       </c>
       <c r="H117" t="n">
         <v>0.952</v>
@@ -7282,7 +7282,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -7315,10 +7315,10 @@
         <v>0.4808</v>
       </c>
       <c r="F118" t="n">
-        <v>0.9424</v>
+        <v>0.9484</v>
       </c>
       <c r="G118" t="n">
-        <v>0.4769</v>
+        <v>0.4902</v>
       </c>
       <c r="H118" t="n">
         <v>0.9544</v>
@@ -7377,10 +7377,10 @@
         <v>0.437</v>
       </c>
       <c r="F119" t="n">
-        <v>0.9316</v>
+        <v>0.9388</v>
       </c>
       <c r="G119" t="n">
-        <v>0.406</v>
+        <v>0.4897</v>
       </c>
       <c r="H119" t="n">
         <v>0.9399999999999999</v>
@@ -7439,10 +7439,10 @@
         <v>0.432</v>
       </c>
       <c r="F120" t="n">
-        <v>0.9376</v>
+        <v>0.9364</v>
       </c>
       <c r="G120" t="n">
-        <v>0.4435</v>
+        <v>0.4469</v>
       </c>
       <c r="H120" t="n">
         <v>0.946</v>
@@ -7582,13 +7582,13 @@
         <v>0.8571</v>
       </c>
       <c r="E123" t="n">
-        <v>0.2183</v>
+        <v>0.218</v>
       </c>
       <c r="F123" t="n">
-        <v>0.8667</v>
+        <v>0.8595</v>
       </c>
       <c r="G123" t="n">
-        <v>0.2654</v>
+        <v>0.2428</v>
       </c>
       <c r="H123" t="n">
         <v>0.8691</v>
@@ -7614,7 +7614,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 10}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>0.1926</v>
       </c>
       <c r="D124" t="n">
-        <v>0.8522999999999999</v>
+        <v>0.8511</v>
       </c>
       <c r="E124" t="n">
-        <v>0.1963</v>
+        <v>0.195</v>
       </c>
       <c r="F124" t="n">
-        <v>0.8511</v>
+        <v>0.8499</v>
       </c>
       <c r="G124" t="n">
-        <v>0.1989</v>
+        <v>0.1732</v>
       </c>
       <c r="H124" t="n">
         <v>0.8535</v>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -7706,13 +7706,13 @@
         <v>0.8391</v>
       </c>
       <c r="E125" t="n">
-        <v>0.1613</v>
+        <v>0.1621</v>
       </c>
       <c r="F125" t="n">
-        <v>0.8487</v>
+        <v>0.8499</v>
       </c>
       <c r="G125" t="n">
-        <v>0.2371</v>
+        <v>0.2349</v>
       </c>
       <c r="H125" t="n">
         <v>0.8522999999999999</v>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 10}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -7771,10 +7771,10 @@
         <v>0.2017</v>
       </c>
       <c r="F126" t="n">
-        <v>0.8631</v>
+        <v>0.8619</v>
       </c>
       <c r="G126" t="n">
-        <v>0.2099</v>
+        <v>0.2595</v>
       </c>
       <c r="H126" t="n">
         <v>0.8643</v>
@@ -7800,7 +7800,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 10}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -7833,10 +7833,10 @@
         <v>0.1731</v>
       </c>
       <c r="F127" t="n">
-        <v>0.8583</v>
+        <v>0.8559</v>
       </c>
       <c r="G127" t="n">
-        <v>0.2145</v>
+        <v>0.2115</v>
       </c>
       <c r="H127" t="n">
         <v>0.8559</v>
@@ -7895,10 +7895,10 @@
         <v>0.2156</v>
       </c>
       <c r="F128" t="n">
-        <v>0.8655</v>
+        <v>0.8643</v>
       </c>
       <c r="G128" t="n">
-        <v>0.2347</v>
+        <v>0.2402</v>
       </c>
       <c r="H128" t="n">
         <v>0.8655</v>
@@ -7957,10 +7957,10 @@
         <v>0.1999</v>
       </c>
       <c r="F129" t="n">
-        <v>0.8619</v>
+        <v>0.8631</v>
       </c>
       <c r="G129" t="n">
-        <v>0.2168</v>
+        <v>0.2086</v>
       </c>
       <c r="H129" t="n">
         <v>0.8667</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -8013,16 +8013,16 @@
         <v>0.1833</v>
       </c>
       <c r="D130" t="n">
-        <v>0.8522999999999999</v>
+        <v>0.8547</v>
       </c>
       <c r="E130" t="n">
-        <v>0.1762</v>
+        <v>0.1755</v>
       </c>
       <c r="F130" t="n">
-        <v>0.8595</v>
+        <v>0.8643</v>
       </c>
       <c r="G130" t="n">
-        <v>0.1961</v>
+        <v>0.2136</v>
       </c>
       <c r="H130" t="n">
         <v>0.8619</v>
@@ -8081,10 +8081,10 @@
         <v>0.1604</v>
       </c>
       <c r="F131" t="n">
-        <v>0.8463000000000001</v>
+        <v>0.8522999999999999</v>
       </c>
       <c r="G131" t="n">
-        <v>0.1864</v>
+        <v>0.1963</v>
       </c>
       <c r="H131" t="n">
         <v>0.8679</v>
@@ -8110,7 +8110,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 5}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -8140,13 +8140,13 @@
         <v>0.8475</v>
       </c>
       <c r="E132" t="n">
-        <v>0.1857</v>
+        <v>0.1855</v>
       </c>
       <c r="F132" t="n">
-        <v>0.8427</v>
+        <v>0.8391</v>
       </c>
       <c r="G132" t="n">
-        <v>0.1733</v>
+        <v>0.1537</v>
       </c>
       <c r="H132" t="n">
         <v>0.8427</v>
@@ -8286,13 +8286,13 @@
         <v>0.7935</v>
       </c>
       <c r="E135" t="n">
-        <v>0.0914</v>
+        <v>0.0912</v>
       </c>
       <c r="F135" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.8043</v>
       </c>
       <c r="G135" t="n">
-        <v>0.1146</v>
+        <v>0.1201</v>
       </c>
       <c r="H135" t="n">
         <v>0.8055</v>
@@ -8345,16 +8345,16 @@
         <v>0.0871</v>
       </c>
       <c r="D136" t="n">
-        <v>0.8115</v>
+        <v>0.8127</v>
       </c>
       <c r="E136" t="n">
-        <v>0.1321</v>
+        <v>0.1372</v>
       </c>
       <c r="F136" t="n">
-        <v>0.8067</v>
+        <v>0.8043</v>
       </c>
       <c r="G136" t="n">
-        <v>0.1051</v>
+        <v>0.1211</v>
       </c>
       <c r="H136" t="n">
         <v>0.8127</v>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 5}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
@@ -8410,13 +8410,13 @@
         <v>0.8055</v>
       </c>
       <c r="E137" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.0954</v>
       </c>
       <c r="F137" t="n">
-        <v>0.8103</v>
+        <v>0.8091</v>
       </c>
       <c r="G137" t="n">
-        <v>0.1142</v>
+        <v>0.1027</v>
       </c>
       <c r="H137" t="n">
         <v>0.8115</v>
@@ -8472,13 +8472,13 @@
         <v>0.7935</v>
       </c>
       <c r="E138" t="n">
-        <v>0.0785</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="F138" t="n">
-        <v>0.8115</v>
+        <v>0.8031</v>
       </c>
       <c r="G138" t="n">
-        <v>0.1382</v>
+        <v>0.1125</v>
       </c>
       <c r="H138" t="n">
         <v>0.8115</v>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
@@ -8531,16 +8531,16 @@
         <v>0.1084</v>
       </c>
       <c r="D139" t="n">
-        <v>0.7959000000000001</v>
+        <v>0.7947</v>
       </c>
       <c r="E139" t="n">
-        <v>0.1126</v>
+        <v>0.1058</v>
       </c>
       <c r="F139" t="n">
-        <v>0.8139</v>
+        <v>0.8127</v>
       </c>
       <c r="G139" t="n">
-        <v>0.1212</v>
+        <v>0.1328</v>
       </c>
       <c r="H139" t="n">
         <v>0.8163</v>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_split': 5}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
@@ -8593,16 +8593,16 @@
         <v>0.1046</v>
       </c>
       <c r="D140" t="n">
-        <v>0.8127</v>
+        <v>0.8115</v>
       </c>
       <c r="E140" t="n">
         <v>0.1016</v>
       </c>
       <c r="F140" t="n">
-        <v>0.8139</v>
+        <v>0.8151</v>
       </c>
       <c r="G140" t="n">
-        <v>0.1296</v>
+        <v>0.1233</v>
       </c>
       <c r="H140" t="n">
         <v>0.8175</v>
@@ -8655,16 +8655,16 @@
         <v>0.105</v>
       </c>
       <c r="D141" t="n">
-        <v>0.8175</v>
+        <v>0.8151</v>
       </c>
       <c r="E141" t="n">
-        <v>0.1333</v>
+        <v>0.1243</v>
       </c>
       <c r="F141" t="n">
-        <v>0.8139</v>
+        <v>0.8091</v>
       </c>
       <c r="G141" t="n">
-        <v>0.1312</v>
+        <v>0.1186</v>
       </c>
       <c r="H141" t="n">
         <v>0.8139</v>
@@ -8723,10 +8723,10 @@
         <v>0.1108</v>
       </c>
       <c r="F142" t="n">
-        <v>0.8175</v>
+        <v>0.8079</v>
       </c>
       <c r="G142" t="n">
-        <v>0.1238</v>
+        <v>0.1081</v>
       </c>
       <c r="H142" t="n">
         <v>0.8199</v>
@@ -8752,7 +8752,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 10}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -8782,13 +8782,13 @@
         <v>0.7983</v>
       </c>
       <c r="E143" t="n">
-        <v>0.0912</v>
+        <v>0.0917</v>
       </c>
       <c r="F143" t="n">
-        <v>0.8031</v>
+        <v>0.8115</v>
       </c>
       <c r="G143" t="n">
-        <v>0.106</v>
+        <v>0.1466</v>
       </c>
       <c r="H143" t="n">
         <v>0.8163</v>
@@ -8814,7 +8814,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 5}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
@@ -8850,7 +8850,7 @@
         <v>0.8103</v>
       </c>
       <c r="G144" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.0945</v>
       </c>
       <c r="H144" t="n">
         <v>0.8139</v>
@@ -8876,7 +8876,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_split': 5}</t>
+          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -8993,10 +8993,10 @@
         <v>0.7971</v>
       </c>
       <c r="F147" t="n">
-        <v>0.976</v>
+        <v>0.9808</v>
       </c>
       <c r="G147" t="n">
-        <v>0.8407</v>
+        <v>0.8665</v>
       </c>
       <c r="H147" t="n">
         <v>0.9868</v>
@@ -9055,10 +9055,10 @@
         <v>0.8144</v>
       </c>
       <c r="F148" t="n">
-        <v>0.982</v>
+        <v>0.9808</v>
       </c>
       <c r="G148" t="n">
-        <v>0.8611</v>
+        <v>0.8207</v>
       </c>
       <c r="H148" t="n">
         <v>0.9844000000000001</v>
@@ -9084,7 +9084,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -9117,10 +9117,10 @@
         <v>0.8145</v>
       </c>
       <c r="F149" t="n">
-        <v>0.982</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="G149" t="n">
-        <v>0.8922</v>
+        <v>0.9085</v>
       </c>
       <c r="H149" t="n">
         <v>0.9916</v>
@@ -9146,7 +9146,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 10}</t>
+          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -9179,10 +9179,10 @@
         <v>0.9254</v>
       </c>
       <c r="F150" t="n">
-        <v>0.9808</v>
+        <v>0.9868</v>
       </c>
       <c r="G150" t="n">
-        <v>0.8747</v>
+        <v>0.9187</v>
       </c>
       <c r="H150" t="n">
         <v>0.994</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -9241,10 +9241,10 @@
         <v>0.7583</v>
       </c>
       <c r="F151" t="n">
-        <v>0.9772</v>
+        <v>0.976</v>
       </c>
       <c r="G151" t="n">
-        <v>0.7891</v>
+        <v>0.7957</v>
       </c>
       <c r="H151" t="n">
         <v>0.9892</v>
@@ -9306,7 +9306,7 @@
         <v>0.9808</v>
       </c>
       <c r="G152" t="n">
-        <v>0.8719</v>
+        <v>0.8663999999999999</v>
       </c>
       <c r="H152" t="n">
         <v>0.9916</v>
@@ -9365,10 +9365,10 @@
         <v>0.841</v>
       </c>
       <c r="F153" t="n">
-        <v>0.9772</v>
+        <v>0.9796</v>
       </c>
       <c r="G153" t="n">
-        <v>0.8024</v>
+        <v>0.7966</v>
       </c>
       <c r="H153" t="n">
         <v>0.9868</v>
@@ -9394,7 +9394,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 10}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -9427,10 +9427,10 @@
         <v>0.8726</v>
       </c>
       <c r="F154" t="n">
-        <v>0.9832</v>
+        <v>0.9748</v>
       </c>
       <c r="G154" t="n">
-        <v>0.9029</v>
+        <v>0.8613</v>
       </c>
       <c r="H154" t="n">
         <v>0.9868</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
@@ -9489,10 +9489,10 @@
         <v>0.8413</v>
       </c>
       <c r="F155" t="n">
-        <v>0.9868</v>
+        <v>0.9856</v>
       </c>
       <c r="G155" t="n">
-        <v>0.896</v>
+        <v>0.8968</v>
       </c>
       <c r="H155" t="n">
         <v>0.988</v>
@@ -9554,7 +9554,7 @@
         <v>0.976</v>
       </c>
       <c r="G156" t="n">
-        <v>0.8817</v>
+        <v>0.8676</v>
       </c>
       <c r="H156" t="n">
         <v>0.9892</v>
@@ -9580,7 +9580,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 5}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
@@ -9697,10 +9697,10 @@
         <v>0.7971</v>
       </c>
       <c r="F159" t="n">
-        <v>0.976</v>
+        <v>0.9808</v>
       </c>
       <c r="G159" t="n">
-        <v>0.8407</v>
+        <v>0.8665</v>
       </c>
       <c r="H159" t="n">
         <v>0.9868</v>
@@ -9759,10 +9759,10 @@
         <v>0.8144</v>
       </c>
       <c r="F160" t="n">
-        <v>0.982</v>
+        <v>0.9808</v>
       </c>
       <c r="G160" t="n">
-        <v>0.8611</v>
+        <v>0.8207</v>
       </c>
       <c r="H160" t="n">
         <v>0.9844000000000001</v>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
@@ -9821,10 +9821,10 @@
         <v>0.8145</v>
       </c>
       <c r="F161" t="n">
-        <v>0.982</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="G161" t="n">
-        <v>0.8922</v>
+        <v>0.9085</v>
       </c>
       <c r="H161" t="n">
         <v>0.9916</v>
@@ -9850,7 +9850,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 10}</t>
+          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
@@ -9883,10 +9883,10 @@
         <v>0.9254</v>
       </c>
       <c r="F162" t="n">
-        <v>0.9808</v>
+        <v>0.9868</v>
       </c>
       <c r="G162" t="n">
-        <v>0.8747</v>
+        <v>0.9187</v>
       </c>
       <c r="H162" t="n">
         <v>0.994</v>
@@ -9912,7 +9912,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
@@ -9945,10 +9945,10 @@
         <v>0.7583</v>
       </c>
       <c r="F163" t="n">
-        <v>0.9772</v>
+        <v>0.976</v>
       </c>
       <c r="G163" t="n">
-        <v>0.7891</v>
+        <v>0.7957</v>
       </c>
       <c r="H163" t="n">
         <v>0.9892</v>
@@ -10010,7 +10010,7 @@
         <v>0.9808</v>
       </c>
       <c r="G164" t="n">
-        <v>0.8719</v>
+        <v>0.8663999999999999</v>
       </c>
       <c r="H164" t="n">
         <v>0.9916</v>
@@ -10069,10 +10069,10 @@
         <v>0.841</v>
       </c>
       <c r="F165" t="n">
-        <v>0.9772</v>
+        <v>0.9796</v>
       </c>
       <c r="G165" t="n">
-        <v>0.8024</v>
+        <v>0.7966</v>
       </c>
       <c r="H165" t="n">
         <v>0.9868</v>
@@ -10098,7 +10098,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 10}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
@@ -10131,10 +10131,10 @@
         <v>0.8726</v>
       </c>
       <c r="F166" t="n">
-        <v>0.9832</v>
+        <v>0.9748</v>
       </c>
       <c r="G166" t="n">
-        <v>0.9029</v>
+        <v>0.8613</v>
       </c>
       <c r="H166" t="n">
         <v>0.9868</v>
@@ -10160,7 +10160,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -10193,10 +10193,10 @@
         <v>0.8413</v>
       </c>
       <c r="F167" t="n">
-        <v>0.9868</v>
+        <v>0.9856</v>
       </c>
       <c r="G167" t="n">
-        <v>0.896</v>
+        <v>0.8968</v>
       </c>
       <c r="H167" t="n">
         <v>0.988</v>
@@ -10258,7 +10258,7 @@
         <v>0.976</v>
       </c>
       <c r="G168" t="n">
-        <v>0.8817</v>
+        <v>0.8676</v>
       </c>
       <c r="H168" t="n">
         <v>0.9892</v>
@@ -10284,7 +10284,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 5}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
@@ -10401,10 +10401,10 @@
         <v>0.7964</v>
       </c>
       <c r="F171" t="n">
-        <v>0.9772</v>
+        <v>0.9748</v>
       </c>
       <c r="G171" t="n">
-        <v>0.7859</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="H171" t="n">
         <v>0.9868</v>
@@ -10430,7 +10430,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 5}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
@@ -10463,10 +10463,10 @@
         <v>0.9001</v>
       </c>
       <c r="F172" t="n">
-        <v>0.9844000000000001</v>
+        <v>0.988</v>
       </c>
       <c r="G172" t="n">
-        <v>0.8518</v>
+        <v>0.9207</v>
       </c>
       <c r="H172" t="n">
         <v>0.994</v>
@@ -10492,7 +10492,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 5}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
@@ -10525,10 +10525,10 @@
         <v>0.8565</v>
       </c>
       <c r="F173" t="n">
-        <v>0.9796</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="G173" t="n">
-        <v>0.8884</v>
+        <v>0.9292</v>
       </c>
       <c r="H173" t="n">
         <v>0.9903999999999999</v>
@@ -10554,7 +10554,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 5}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
@@ -10587,10 +10587,10 @@
         <v>0.8162</v>
       </c>
       <c r="F174" t="n">
-        <v>0.982</v>
+        <v>0.9796</v>
       </c>
       <c r="G174" t="n">
-        <v>0.8669</v>
+        <v>0.84</v>
       </c>
       <c r="H174" t="n">
         <v>0.988</v>
@@ -10616,7 +10616,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 5}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
@@ -10649,10 +10649,10 @@
         <v>0.825</v>
       </c>
       <c r="F175" t="n">
-        <v>0.9736</v>
+        <v>0.9772</v>
       </c>
       <c r="G175" t="n">
-        <v>0.8005</v>
+        <v>0.8001</v>
       </c>
       <c r="H175" t="n">
         <v>0.9892</v>
@@ -10678,7 +10678,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 5}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
@@ -10711,10 +10711,10 @@
         <v>0.8062</v>
       </c>
       <c r="F176" t="n">
-        <v>0.9844000000000001</v>
+        <v>0.982</v>
       </c>
       <c r="G176" t="n">
-        <v>0.8628</v>
+        <v>0.835</v>
       </c>
       <c r="H176" t="n">
         <v>0.988</v>
@@ -10740,7 +10740,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
@@ -10773,10 +10773,10 @@
         <v>0.8345</v>
       </c>
       <c r="F177" t="n">
-        <v>0.9748</v>
+        <v>0.9784</v>
       </c>
       <c r="G177" t="n">
-        <v>0.8245</v>
+        <v>0.851</v>
       </c>
       <c r="H177" t="n">
         <v>0.9892</v>
@@ -10838,7 +10838,7 @@
         <v>0.9784</v>
       </c>
       <c r="G178" t="n">
-        <v>0.8455</v>
+        <v>0.8341</v>
       </c>
       <c r="H178" t="n">
         <v>0.9903999999999999</v>
@@ -10897,10 +10897,10 @@
         <v>0.8241000000000001</v>
       </c>
       <c r="F179" t="n">
-        <v>0.976</v>
+        <v>0.9736</v>
       </c>
       <c r="G179" t="n">
-        <v>0.7986</v>
+        <v>0.8084</v>
       </c>
       <c r="H179" t="n">
         <v>0.9892</v>
@@ -10926,7 +10926,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 5}</t>
+          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
@@ -10962,7 +10962,7 @@
         <v>0.9844000000000001</v>
       </c>
       <c r="G180" t="n">
-        <v>0.9119</v>
+        <v>0.8892</v>
       </c>
       <c r="H180" t="n">
         <v>0.9868</v>
@@ -10988,7 +10988,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 5}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
@@ -11105,10 +11105,10 @@
         <v>0.7964</v>
       </c>
       <c r="F183" t="n">
-        <v>0.9772</v>
+        <v>0.9748</v>
       </c>
       <c r="G183" t="n">
-        <v>0.7859</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="H183" t="n">
         <v>0.9868</v>
@@ -11134,7 +11134,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 5}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
@@ -11167,10 +11167,10 @@
         <v>0.9001</v>
       </c>
       <c r="F184" t="n">
-        <v>0.9844000000000001</v>
+        <v>0.988</v>
       </c>
       <c r="G184" t="n">
-        <v>0.8518</v>
+        <v>0.9207</v>
       </c>
       <c r="H184" t="n">
         <v>0.994</v>
@@ -11196,7 +11196,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 5}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
@@ -11229,10 +11229,10 @@
         <v>0.8565</v>
       </c>
       <c r="F185" t="n">
-        <v>0.9796</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="G185" t="n">
-        <v>0.8884</v>
+        <v>0.9292</v>
       </c>
       <c r="H185" t="n">
         <v>0.9903999999999999</v>
@@ -11258,7 +11258,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 5}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 5}</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
@@ -11291,10 +11291,10 @@
         <v>0.8162</v>
       </c>
       <c r="F186" t="n">
-        <v>0.982</v>
+        <v>0.9796</v>
       </c>
       <c r="G186" t="n">
-        <v>0.8669</v>
+        <v>0.84</v>
       </c>
       <c r="H186" t="n">
         <v>0.988</v>
@@ -11320,7 +11320,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 5}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
@@ -11353,10 +11353,10 @@
         <v>0.825</v>
       </c>
       <c r="F187" t="n">
-        <v>0.9736</v>
+        <v>0.9772</v>
       </c>
       <c r="G187" t="n">
-        <v>0.8005</v>
+        <v>0.8001</v>
       </c>
       <c r="H187" t="n">
         <v>0.9892</v>
@@ -11382,7 +11382,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 5}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
@@ -11415,10 +11415,10 @@
         <v>0.8062</v>
       </c>
       <c r="F188" t="n">
-        <v>0.9844000000000001</v>
+        <v>0.982</v>
       </c>
       <c r="G188" t="n">
-        <v>0.8628</v>
+        <v>0.835</v>
       </c>
       <c r="H188" t="n">
         <v>0.988</v>
@@ -11444,7 +11444,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
@@ -11477,10 +11477,10 @@
         <v>0.8345</v>
       </c>
       <c r="F189" t="n">
-        <v>0.9748</v>
+        <v>0.9784</v>
       </c>
       <c r="G189" t="n">
-        <v>0.8245</v>
+        <v>0.851</v>
       </c>
       <c r="H189" t="n">
         <v>0.9892</v>
@@ -11542,7 +11542,7 @@
         <v>0.9784</v>
       </c>
       <c r="G190" t="n">
-        <v>0.8455</v>
+        <v>0.8341</v>
       </c>
       <c r="H190" t="n">
         <v>0.9903999999999999</v>
@@ -11601,10 +11601,10 @@
         <v>0.8241000000000001</v>
       </c>
       <c r="F191" t="n">
-        <v>0.976</v>
+        <v>0.9736</v>
       </c>
       <c r="G191" t="n">
-        <v>0.7986</v>
+        <v>0.8084</v>
       </c>
       <c r="H191" t="n">
         <v>0.9892</v>
@@ -11630,7 +11630,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_split': 5}</t>
+          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
@@ -11666,7 +11666,7 @@
         <v>0.9844000000000001</v>
       </c>
       <c r="G192" t="n">
-        <v>0.9119</v>
+        <v>0.8892</v>
       </c>
       <c r="H192" t="n">
         <v>0.9868</v>
@@ -11692,7 +11692,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 5}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
@@ -11729,17 +11729,17 @@
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>0.6888 ± 0.2627</t>
+          <t>0.6888 ± 0.2628</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>0.9511 ± 0.0602</t>
+          <t>0.9511 ± 0.0606</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr">
         <is>
-          <t>0.7335 ± 0.2828</t>
+          <t>0.7341 ± 0.2823</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr">
@@ -24583,8 +24583,8 @@
     <mergeCell ref="B121:R121"/>
     <mergeCell ref="B181:R181"/>
     <mergeCell ref="B157:R157"/>
+    <mergeCell ref="B97:R97"/>
     <mergeCell ref="B13:R13"/>
-    <mergeCell ref="B97:R97"/>
     <mergeCell ref="B145:R145"/>
     <mergeCell ref="B73:R73"/>
     <mergeCell ref="B109:R109"/>
